--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.89476552601854</v>
+        <v>9.895399397978013</v>
       </c>
       <c r="D2" t="n">
-        <v>60.65194919908361</v>
+        <v>9.855941744851087</v>
       </c>
       <c r="E2" t="n">
-        <v>13.79197142401035</v>
+        <v>2.241195356401683</v>
       </c>
       <c r="F2" t="n">
-        <v>15.2412834582019</v>
+        <v>2.476708561957808</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.28361321280771</v>
+        <v>4.271087147081253</v>
       </c>
       <c r="D3" t="n">
-        <v>25.61995089431264</v>
+        <v>4.163242020325804</v>
       </c>
       <c r="E3" t="n">
-        <v>13.79197142401035</v>
+        <v>2.241195356401683</v>
       </c>
       <c r="F3" t="n">
-        <v>15.2412834582019</v>
+        <v>2.476708561957808</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>69.84590428869127</v>
+        <v>11.34995944691233</v>
       </c>
       <c r="D4" t="n">
-        <v>51.41984052872976</v>
+        <v>8.355724085918586</v>
       </c>
       <c r="E4" t="n">
-        <v>13.79197142401035</v>
+        <v>2.241195356401683</v>
       </c>
       <c r="F4" t="n">
-        <v>15.2412834582019</v>
+        <v>2.476708561957808</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.1059861353328</v>
+        <v>7.81722274699158</v>
       </c>
       <c r="D5" t="n">
-        <v>26.65616289731445</v>
+        <v>4.331626470813598</v>
       </c>
       <c r="E5" t="n">
-        <v>13.79197142401035</v>
+        <v>2.241195356401683</v>
       </c>
       <c r="F5" t="n">
-        <v>15.2412834582019</v>
+        <v>2.476708561957808</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.29520574491048</v>
+        <v>8.172970933547953</v>
       </c>
       <c r="D6" t="n">
-        <v>50.11371619046129</v>
+        <v>8.14347888094996</v>
       </c>
       <c r="E6" t="n">
-        <v>13.79197142401035</v>
+        <v>2.241195356401683</v>
       </c>
       <c r="F6" t="n">
-        <v>15.2412834582019</v>
+        <v>2.476708561957808</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>68.51539301753131</v>
+        <v>11.13375136534884</v>
       </c>
       <c r="D7" t="n">
-        <v>68.70802964308307</v>
+        <v>11.165054817001</v>
       </c>
       <c r="E7" t="n">
-        <v>13.79197142401035</v>
+        <v>2.241195356401683</v>
       </c>
       <c r="F7" t="n">
-        <v>15.2412834582019</v>
+        <v>2.476708561957808</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.53240921715859</v>
+        <v>9.186516497788272</v>
       </c>
       <c r="D8" t="n">
-        <v>56.13340322920961</v>
+        <v>9.121678024746563</v>
       </c>
       <c r="E8" t="n">
-        <v>13.79197142401035</v>
+        <v>2.241195356401683</v>
       </c>
       <c r="F8" t="n">
-        <v>15.2412834582019</v>
+        <v>2.476708561957808</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
